--- a/光伏配储项目/电价数据/2026/岚影站.xlsx
+++ b/光伏配储项目/电价数据/2026/岚影站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5171</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.76285</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.58074</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.57698</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.51612</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.52461</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43464</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45098</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42511</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.41908</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41821</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4064</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39465</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38305</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.41993</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.40992</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41464</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41165</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42153</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.40999</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.4398</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.48871</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.39477</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.27818</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.03828</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.04663</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.25901</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.01842</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.06784</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.0479</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.20283</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.26182</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.02587</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.12268</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.14557</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.20435</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.20969</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.19356</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.00821</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.0407</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.02931</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.21169</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.18194</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.46395</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5745399999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.51664</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7335499999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.08557</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39493</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.9749500000000001</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43202</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43731</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.66012</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.8277100000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.43649</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.16176</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.67212</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.0642</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.24526</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.40147</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.64654</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6978099999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.23095</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8756900000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7983</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75924</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51893</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48129</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47066</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41658</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42634</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71289</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.78859</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8765700000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9241200000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49727</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5192899999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50578</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50602</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4881</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37218</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38308</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4247</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.9956799999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.84129</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.9221</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.47165</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.45862</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38441</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42307</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50714</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.27426</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.25911</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.22065</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.1703</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.63966</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.84021</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.17148</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.8281000000000001</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.76362</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.27476</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.74433</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.9692799999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.04984</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.40087</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.44518</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.49406</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.7838999999999999</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6274299999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.76866</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.78583</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.15904</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.24678</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.18181</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.85261</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20345</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.10447</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25714</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.03284</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.08942</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.64547</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.98238</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90659</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.96892</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.83514</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.93877</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.77115</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.753</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45159</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.76402</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.78588</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45022</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42915</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44484</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33476</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51044</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48905</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.49055</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42965</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.4454</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38646</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47473</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44526</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4397799999999999</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39546</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.4372</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.42345</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.15412</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.07914</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.09225</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.01539</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.01872</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.29968</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.19062</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.67023</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.02079</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.59539</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.6682</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.50958</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.41093</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.80679</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.6216</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.60377</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.48975</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.4705</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.12829</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.43135</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39652</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.47307</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.47552</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.48242</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5510499999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5576599999999999</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.49607</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5179199999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.27897</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6191599999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.61572</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46336</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50649</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.51503</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6022799999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.56196</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.6233500000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.45451</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42438</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61403</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.6264400000000001</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56163</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.75262</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.63164</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.54657</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.4607</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.59536</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44472</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45779</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34212</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52634</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44796</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38772</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45032</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41582</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.42676</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40574</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.2434</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.21954</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28681</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.22645</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6177</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.59137</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.45367</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.20156</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.2829100000000001</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.49385</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.42392</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6086</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.47098</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.39431</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28824</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.48833</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.48769</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.43539</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.50014</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45004</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46415</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47515</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.50892</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.5679099999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.44101</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.5549299999999999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.47422</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45887</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.49983</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42235</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41723</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32113</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.42275</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.25074</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.16935</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.21757</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.19127</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15441</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.25198</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.05384000000000001</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.19609</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.01533</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.16483</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.1289</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.15719</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00456</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27402</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.39231</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39621</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40417</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.40333</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40313</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.50693</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35365</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.68229</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.46252</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.43733</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.43907</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10247</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.0434</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04472</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01793</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.22131</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05678</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.21295</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.01642</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07545</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.07371</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36851</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33699</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31792</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4079700000000001</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42827</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45655</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78534</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8629</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88752</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.1871</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86818</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.50278</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33087</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03293</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307999999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52179</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77299</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77755</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49316</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39991</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20701</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62187</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44999</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41981</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43653</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45129</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40299</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40623</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.59687</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.44334</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.6000599999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.74566</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87948</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46888</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.42843</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5921000000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45702</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.89746</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.65044</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.86351</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87497</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.45064</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.7239</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.71889</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59984</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29583</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41869</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.42151</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.46391</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.42404</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.38184</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35585</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47352</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.43771</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41542</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47688</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41765</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40886</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.51491</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.39497</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37656</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.15585</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27202</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19918</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25601</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27688</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.45505</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42379</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.45311</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42779</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.6211</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89766</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.47388</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16542</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70394</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7948999999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65491</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.60997</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.4699700000000001</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45409</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50454</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44354</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.4457</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41619</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.43103</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.51597</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41614</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43751</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.42254</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43755</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.4396</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.46379</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42663</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.44595</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41614</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40944</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.43535</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49795</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.37533</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37384</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5629</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.16111</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.28098</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27637</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.00116</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26195</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25582</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28316</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40992</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36905</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5814900000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.47397</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.86695</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.47678</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.45009</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.4697</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32977</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43499</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.40711</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.41609</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.2854</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22458</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.12807</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.12961</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27789</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.13669</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.12913</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.12858</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.25709</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13096</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24372</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.12825</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25251</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28412</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.18963</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.10849</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.08810999999999999</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10597</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.11194</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.18946</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.1266</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27572</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4617</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39763</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.40469</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4644</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.45187</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.45071</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.45586</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35439</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.55791</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39115</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.48204</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.42489</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38795</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.46319</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29614</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27107</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.27718</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.22925</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.26183</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23906</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.21464</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30202</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.25466</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28712</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24423</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.53603</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.42881</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.28348</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38402</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.42711</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36493</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.52176</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37303</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5325700000000001</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38623</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.38833</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3909</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.40651</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.20862</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.37827</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.68437</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.45996</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.56847</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.63798</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.61619</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.6021799999999999</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42955</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.39679</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.42975</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24188</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.23304</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.40826</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.75713</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.51781</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.72785</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.5661</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.7978</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.51027</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.6448700000000001</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.40821</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.41514</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.6235299999999999</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.45908</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.39942</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44155</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42355</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69675</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.79888</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.71265</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5947100000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.51275</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.25175</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.41612</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.35556</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.44145</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42567</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.36655</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38278</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28622</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.43049</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.41341</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38882</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.35225</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.39254</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38983</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4347200000000001</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38467</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65918</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.82331</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.4625</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.47123</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.4447</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34834</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25748</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.12564</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.18947</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.41333</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27718</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.20881</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25045</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28225</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27437</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28798</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.42174</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40235</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.64177</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5998300000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5981000000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.49749</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.80787</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48947</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8313200000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.43255</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48722</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42547</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36292</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.5123099999999999</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.61187</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.54098</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.73861</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.43062</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.43146</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.41462</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.42351</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.43023</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40989</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.42134</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41922</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.40369</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.43449</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.43236</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.41398</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.42727</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.47481</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.47107</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.59875</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.47077</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.52339</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.46833</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47838</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.41464</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.46174</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.49825</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.49423</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.57824</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43856</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3873</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.42322</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.41496</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42122</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.65124</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.42419</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.8729199999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.38385</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.40772</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42582</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.45276</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.5164500000000001</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.46902</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5394099999999999</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.54091</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.58709</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.75718</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.9145800000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.0069</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.71373</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8745000000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.7434299999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5787899999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.9043600000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.77467</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62776</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67671</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.48729</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.5079399999999999</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.50642</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.49935</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.49195</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.43093</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.58461</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.44332</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.45914</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.47561</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42853</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.46432</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42027</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.48217</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.41339</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.42091</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.40588</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38708</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.38279</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.43061</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.40211</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40337</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.40545</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.39072</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.5254099999999999</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.23665</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.27559</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.42668</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.41322</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40651</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.48391</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.42046</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.08228000000000001</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.17106</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.18186</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.40668</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.43616</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43765</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42159</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.46573</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.41225</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.42496</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.41029</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.41682</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.43433</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.42959</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.41444</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.41585</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.41007</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.38655</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.38774</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.42537</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.40945</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.38839</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.5284099999999999</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.41053</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.4247</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.41716</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.40218</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.43349</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.41122</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.40725</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.41334</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.37892</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.37658</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.39794</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.25519</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28955</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.21867</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24003</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.23881</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.17315</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24547</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04945</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29338</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27721</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.15099</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.17185</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22182</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24978</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26476</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.22929</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28514</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.39723</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.3954</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.39615</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35952</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.22885</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.27453</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27873</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01996</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00065</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14741</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02072</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03956</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01508</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04278</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04065</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04857</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04822</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02915</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04939</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27371</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03841</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01756</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.0361</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20186</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26449</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28846</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.45716</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.38645</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.35239</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.87264</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.73526</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.41613</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.57512</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.43374</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.45342</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.40391</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.41908</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.40758</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.43813</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.44386</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.41374</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.9477100000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.02251</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.88227</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8430299999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.1009</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.14888</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.1974</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.16464</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.18292</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.16285</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.01303</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.13222</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.01968</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.15053</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.01706</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30223</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.16263</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.01755</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.15644</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.17855</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25474</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.44247</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.40918</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.38426</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.41081</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.77256</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.87618</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.89212</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.88573</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.51874</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.8885299999999999</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.90555</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.91275</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84768</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.84585</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8502000000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9471799999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.88461</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.90865</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.88458</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.38352</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.51332</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.70545</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.92601</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.66151</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.50143</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.5165700000000001</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.4421</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.43555</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.41159</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.41588</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.55675</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.39734</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.41059</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.41448</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.51552</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.54167</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.4323</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41326</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.42697</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.37495</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.40632</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.23147</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.53584</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.49386</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.55352</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.56441</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26204</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.5627799999999999</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.40431</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.43435</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.51627</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.9212100000000001</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.71427</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.5161399999999999</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.40432</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.4689700000000001</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.46037</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.42829</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.55175</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.38428</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.36368</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.45935</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.43816</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.41183</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.38262</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3742200000000001</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.37374</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.46268</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.39413</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.38104</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.67173</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.8551599999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.65391</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.7411599999999999</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.60409</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.54915</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.76705</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.81828</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.51148</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.43902</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5121100000000001</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5472400000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.60214</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8259299999999999</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.50585</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.8029299999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.6550900000000001</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.51777</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.5185700000000001</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43055</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.41194</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.45351</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40654</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40748</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38372</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.25407</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48392</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40578</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40692</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36558</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.4066</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3767200000000001</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43536</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.38648</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.29763</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29257</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38879</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.38798</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42941</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.6940499999999999</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.77216</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.70477</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.85497</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.09836</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.84836</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.53947</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.79664</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.71288</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.5803700000000001</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.14938</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.8387</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.44581</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.23541</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.13283</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.86783</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.42211</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.45938</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37717</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37662</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37287</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.40178</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38622</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.20541</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.28907</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.18928</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.18933</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.25843</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.09895999999999999</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27035</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.13183</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.25812</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.1537</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.14619</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.17344</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.09973</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.24628</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.20462</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.22368</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.4036</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.51663</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42464</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.42994</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.47256</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.45544</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.43914</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.40635</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42872</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.40523</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.41692</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4356</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38468</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.06036</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.04368</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.63914</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.44394</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.6979</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.42944</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.38286</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.38698</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37642</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37317</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.5766699999999999</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.57224</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.55548</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.36411</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.25261</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.52328</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.6098300000000001</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.9627100000000001</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.60302</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.74533</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.55399</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.52962</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.56011</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.5479299999999999</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.56737</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.39478</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44833</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41488</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40964</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37535</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39263</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.39029</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.36784</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.39671</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38928</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42705</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37036</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.43346</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39514</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.38513</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38174</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.37353</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17497</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14467</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19706</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.08376</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28281</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.01497</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.07676999999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.22262</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.15228</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.18992</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.15958</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.10342</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.23145</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.2053</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.21154</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22554</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26321</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15477</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.08647000000000001</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.20077</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19722</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.1442</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27285</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25558</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.41074</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.38795</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.39238</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38891</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40865</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.48367</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40161</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39708</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39361</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.39313</v>
       </c>
     </row>
   </sheetData>
